--- a/artfynd/A 56742-2025 artfynd.xlsx
+++ b/artfynd/A 56742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74177354</v>
+        <v>74177352</v>
       </c>
       <c r="B2" t="n">
-        <v>97767</v>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1982-12-31</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5D1c 3725. SOM: Dryopteris cristata. LEG: Nadja Niordson. KOM: Det. TK</t>
+          <t>Smålands flora 2007: KOO: 5D1c 3725. SOM: Dryopteris cristata. LEG: Nadja Niordson</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 56742-2025 artfynd.xlsx
+++ b/artfynd/A 56742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,8 +788,16 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74177352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>